--- a/Assets/Resources/MasterData/ItemData.xlsx
+++ b/Assets/Resources/MasterData/ItemData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ゲーム開発Ⅳ\UnityProject\2DRoguelikeSubject\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB09B990-1ADD-43EB-87AB-4A5D2140CB24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDD41E0F-7658-4A27-80F3-70DD75B1F194}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12675" yWindow="-15210" windowWidth="12465" windowHeight="14760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="135" yWindow="-15615" windowWidth="12465" windowHeight="14760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ItemData" sheetId="1" r:id="rId1"/>
@@ -49,10 +49,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>effectID</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>薬</t>
     <rPh sb="0" eb="1">
       <t>クスリ</t>
@@ -78,6 +74,10 @@
   </si>
   <si>
     <t>select</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>actionID</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -433,7 +433,7 @@
     <col min="2" max="2" width="8.125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -447,10 +447,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -466,7 +466,7 @@
         <v>0</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E2" s="2">
         <v>0</v>
@@ -485,7 +485,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E3" s="2">
         <v>0</v>
@@ -504,7 +504,7 @@
         <v>2</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E4" s="2">
         <v>0</v>
@@ -523,7 +523,7 @@
         <v>0</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E5" s="2">
         <v>0</v>
@@ -542,7 +542,7 @@
         <v>0</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E6" s="2">
         <v>0</v>
@@ -561,7 +561,7 @@
         <v>0</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E7" s="2">
         <v>0</v>
@@ -580,7 +580,7 @@
         <v>0</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E8" s="2">
         <v>0</v>
@@ -599,7 +599,7 @@
         <v>0</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E9" s="2">
         <v>0</v>
@@ -618,7 +618,7 @@
         <v>0</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E10" s="2">
         <v>0</v>
@@ -637,7 +637,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E11" s="2">
         <v>0</v>
@@ -656,7 +656,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E12" s="2">
         <v>0</v>
@@ -688,7 +688,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1">
         <v>0</v>
@@ -696,7 +696,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -704,7 +704,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3">
         <v>2</v>

--- a/Assets/Resources/MasterData/ItemData.xlsx
+++ b/Assets/Resources/MasterData/ItemData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ゲーム開発Ⅳ\UnityProject\2DRoguelikeSubject\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDD41E0F-7658-4A27-80F3-70DD75B1F194}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AD8C639-D3F2-45E8-A217-A568B1E69119}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="135" yWindow="-15615" windowWidth="12465" windowHeight="14760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11340" yWindow="-15495" windowWidth="10095" windowHeight="14760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ItemData" sheetId="1" r:id="rId1"/>
@@ -469,7 +469,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -507,7 +507,7 @@
         <v>5</v>
       </c>
       <c r="E4" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:5">

--- a/Assets/Resources/MasterData/ItemData.xlsx
+++ b/Assets/Resources/MasterData/ItemData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ゲーム開発Ⅳ\UnityProject\2DRoguelikeSubject\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AD8C639-D3F2-45E8-A217-A568B1E69119}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BEAC61C-223F-4617-B101-29A76CA52A4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11340" yWindow="-15495" windowWidth="10095" windowHeight="14760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9990" yWindow="-15615" windowWidth="8025" windowHeight="14760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ItemData" sheetId="1" r:id="rId1"/>
@@ -488,7 +488,7 @@
         <v>4</v>
       </c>
       <c r="E3" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -507,7 +507,7 @@
         <v>5</v>
       </c>
       <c r="E4" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">

--- a/Assets/Resources/MasterData/ItemData.xlsx
+++ b/Assets/Resources/MasterData/ItemData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ゲーム開発Ⅳ\UnityProject\2DRoguelikeSubject\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BEAC61C-223F-4617-B101-29A76CA52A4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B376907D-D6B2-493C-B381-695EDB6770F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9990" yWindow="-15615" windowWidth="8025" windowHeight="14760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="465" yWindow="-15270" windowWidth="11100" windowHeight="14760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ItemData" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="12">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -78,6 +78,22 @@
   </si>
   <si>
     <t>actionID</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>minCount</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>maxCount</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>burnID</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>rotID</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -115,7 +131,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -138,14 +154,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -426,17 +454,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="3.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -452,8 +484,20 @@
       <c r="E1" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="2">
         <v>0</v>
       </c>
@@ -471,14 +515,26 @@
       <c r="E2" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="F2" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G2" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H2" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I2" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="2">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="B3" s="2">
-        <f t="shared" ref="B3:B12" si="0">2000+A3</f>
-        <v>2001</v>
+        <f t="shared" ref="B3:B7" si="0">2000+A3</f>
+        <v>2100</v>
       </c>
       <c r="C3" s="2">
         <f>VLOOKUP(D3,reference!A:B,2,FALSE)</f>
@@ -490,176 +546,141 @@
       <c r="E3" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
+      <c r="F3" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G3" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H3" s="2">
+        <v>101</v>
+      </c>
+      <c r="I3" s="2">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="2">
-        <v>2</v>
+        <v>101</v>
       </c>
       <c r="B4" s="2">
-        <f t="shared" si="0"/>
-        <v>2002</v>
+        <f t="shared" ref="B4" si="1">2000+A4</f>
+        <v>2101</v>
       </c>
       <c r="C4" s="2">
         <f>VLOOKUP(D4,reference!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="2">
         <v>2</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+      <c r="F4" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G4" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H4" s="2">
+        <v>103</v>
+      </c>
+      <c r="I4" s="2">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="2">
-        <v>3</v>
+        <v>102</v>
       </c>
       <c r="B5" s="2">
-        <f t="shared" si="0"/>
-        <v>2003</v>
+        <f t="shared" ref="B5" si="2">2000+A5</f>
+        <v>2102</v>
       </c>
       <c r="C5" s="2">
         <f>VLOOKUP(D5,reference!A:B,2,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E5" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+        <v>2</v>
+      </c>
+      <c r="F5" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G5" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H5" s="2">
+        <v>101</v>
+      </c>
+      <c r="I5" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="2">
-        <v>4</v>
+        <v>103</v>
       </c>
       <c r="B6" s="2">
-        <f t="shared" si="0"/>
-        <v>2004</v>
+        <f t="shared" ref="B6" si="3">2000+A6</f>
+        <v>2103</v>
       </c>
       <c r="C6" s="2">
         <f>VLOOKUP(D6,reference!A:B,2,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E6" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+        <v>2</v>
+      </c>
+      <c r="F6" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G6" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H6" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I6" s="2">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="2">
-        <v>5</v>
+        <v>200</v>
       </c>
       <c r="B7" s="2">
         <f t="shared" si="0"/>
-        <v>2005</v>
+        <v>2200</v>
       </c>
       <c r="C7" s="2">
         <f>VLOOKUP(D7,reference!A:B,2,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7" s="2">
         <v>3</v>
       </c>
-      <c r="E7" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="2">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2">
-        <f t="shared" si="0"/>
-        <v>2006</v>
-      </c>
-      <c r="C8" s="2">
-        <f>VLOOKUP(D8,reference!A:B,2,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D8" s="2" t="s">
+      <c r="F7" s="2">
         <v>3</v>
       </c>
-      <c r="E8" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="2">
+      <c r="G7" s="2">
         <v>7</v>
       </c>
-      <c r="B9" s="2">
-        <f t="shared" si="0"/>
-        <v>2007</v>
-      </c>
-      <c r="C9" s="2">
-        <f>VLOOKUP(D9,reference!A:B,2,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E9" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="2">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2">
-        <f t="shared" si="0"/>
-        <v>2008</v>
-      </c>
-      <c r="C10" s="2">
-        <f>VLOOKUP(D10,reference!A:B,2,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="2">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2">
-        <f t="shared" si="0"/>
-        <v>2009</v>
-      </c>
-      <c r="C11" s="2">
-        <f>VLOOKUP(D11,reference!A:B,2,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E11" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="2">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2">
-        <f t="shared" si="0"/>
-        <v>2010</v>
-      </c>
-      <c r="C12" s="2">
-        <f>VLOOKUP(D12,reference!A:B,2,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E12" s="2">
-        <v>0</v>
+      <c r="H7" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I7" s="2">
+        <v>-1</v>
       </c>
     </row>
   </sheetData>
@@ -673,7 +694,7 @@
           <x14:formula1>
             <xm:f>reference!$A:$A</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D12</xm:sqref>
+          <xm:sqref>D2:D7</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/Assets/Resources/MasterData/ItemData.xlsx
+++ b/Assets/Resources/MasterData/ItemData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ゲーム開発Ⅳ\UnityProject\2DRoguelikeSubject\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B376907D-D6B2-493C-B381-695EDB6770F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0345913-6E23-4E69-9DF4-076A1AD3449B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="465" yWindow="-15270" windowWidth="11100" windowHeight="14760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ItemData" sheetId="1" r:id="rId1"/>

--- a/Assets/Resources/MasterData/ItemData.xlsx
+++ b/Assets/Resources/MasterData/ItemData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ゲーム開発Ⅳ\UnityProject\2DRoguelikeSubject\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0345913-6E23-4E69-9DF4-076A1AD3449B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E460F8E-28DE-440F-AC06-EB21983F979B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -575,7 +575,7 @@
         <v>4</v>
       </c>
       <c r="E4" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F4" s="2">
         <v>-1</v>
@@ -606,7 +606,7 @@
         <v>4</v>
       </c>
       <c r="E5" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F5" s="2">
         <v>-1</v>
@@ -637,7 +637,7 @@
         <v>4</v>
       </c>
       <c r="E6" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F6" s="2">
         <v>-1</v>

--- a/Assets/Resources/MasterData/ItemData.xlsx
+++ b/Assets/Resources/MasterData/ItemData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ゲーム開発Ⅳ\UnityProject\2DRoguelikeSubject\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E460F8E-28DE-440F-AC06-EB21983F979B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B97A4840-4BAD-41AE-B20C-8728C15F36D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="18">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -94,6 +94,45 @@
   </si>
   <si>
     <t>rotID</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>巻物</t>
+    <rPh sb="0" eb="2">
+      <t>マキモノ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>バッグ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>投げ物</t>
+    <rPh sb="0" eb="1">
+      <t>ナ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>モノ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>武器</t>
+    <rPh sb="0" eb="2">
+      <t>ブキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>防具</t>
+    <rPh sb="0" eb="2">
+      <t>ボウグ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>equipValue</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -169,11 +208,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -454,7 +494,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="4.5" bestFit="1" customWidth="1"/>
@@ -466,9 +506,10 @@
     <col min="7" max="7" width="10.125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="5.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -496,8 +537,11 @@
       <c r="I1" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:9">
+      <c r="J1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" s="2">
         <v>0</v>
       </c>
@@ -527,8 +571,11 @@
       <c r="I2" s="2">
         <v>-1</v>
       </c>
-    </row>
-    <row r="3" spans="1:9">
+      <c r="J2" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" s="2">
         <v>100</v>
       </c>
@@ -558,8 +605,11 @@
       <c r="I3" s="2">
         <v>102</v>
       </c>
-    </row>
-    <row r="4" spans="1:9">
+      <c r="J3" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" s="2">
         <v>101</v>
       </c>
@@ -589,8 +639,11 @@
       <c r="I4" s="2">
         <v>102</v>
       </c>
-    </row>
-    <row r="5" spans="1:9">
+      <c r="J4" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" s="2">
         <v>102</v>
       </c>
@@ -620,8 +673,11 @@
       <c r="I5" s="2">
         <v>-1</v>
       </c>
-    </row>
-    <row r="6" spans="1:9">
+      <c r="J5" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" s="2">
         <v>103</v>
       </c>
@@ -651,8 +707,11 @@
       <c r="I6" s="2">
         <v>102</v>
       </c>
-    </row>
-    <row r="7" spans="1:9">
+      <c r="J6" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" s="2">
         <v>200</v>
       </c>
@@ -681,6 +740,77 @@
       </c>
       <c r="I7" s="2">
         <v>-1</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="2">
+        <v>600</v>
+      </c>
+      <c r="B8" s="2">
+        <f t="shared" ref="B8" si="4">2000+A8</f>
+        <v>2600</v>
+      </c>
+      <c r="C8" s="2">
+        <f>VLOOKUP(D8,reference!A:B,2,FALSE)</f>
+        <v>6</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="2">
+        <v>-1</v>
+      </c>
+      <c r="F8" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G8" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H8" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I8" s="2">
+        <v>-1</v>
+      </c>
+      <c r="J8" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="2">
+        <v>700</v>
+      </c>
+      <c r="B9" s="2">
+        <f t="shared" ref="B9" si="5">2000+A9</f>
+        <v>2700</v>
+      </c>
+      <c r="C9" s="2">
+        <f>VLOOKUP(D9,reference!A:B,2,FALSE)</f>
+        <v>7</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="2">
+        <v>-1</v>
+      </c>
+      <c r="F9" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G9" s="2">
+        <v>-1</v>
+      </c>
+      <c r="H9" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I9" s="2">
+        <v>-1</v>
+      </c>
+      <c r="J9" s="4">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -694,7 +824,7 @@
           <x14:formula1>
             <xm:f>reference!$A:$A</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D7</xm:sqref>
+          <xm:sqref>D2:D9</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -704,7 +834,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{140304DB-BBA9-40DF-8527-305A594DFD94}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -731,8 +861,49 @@
         <v>2</v>
       </c>
     </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Assets/Resources/MasterData/ItemData.xlsx
+++ b/Assets/Resources/MasterData/ItemData.xlsx
@@ -8,14 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ゲーム開発Ⅳ\UnityProject\2DRoguelikeSubject\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B97A4840-4BAD-41AE-B20C-8728C15F36D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7617BFBD-5C3D-4F6A-AA80-E113EF63BBFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="555" yWindow="-15135" windowWidth="15870" windowHeight="4350" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ItemData" sheetId="1" r:id="rId1"/>
     <sheet name="reference" sheetId="2" r:id="rId2"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId3"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -35,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="19">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -133,6 +136,10 @@
   </si>
   <si>
     <t>equipValue</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>comment</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -156,7 +163,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -166,6 +173,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -208,12 +221,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -229,6 +243,357 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="MessageData"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="1">
+          <cell r="A1" t="str">
+            <v>ID</v>
+          </cell>
+          <cell r="B1" t="str">
+            <v>Message[]</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="A2">
+            <v>0</v>
+          </cell>
+          <cell r="B2" t="str">
+            <v>{0} に {1} ダメージ</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="A3">
+            <v>1</v>
+          </cell>
+          <cell r="B3" t="str">
+            <v>{0} のHPが {1} 回復した</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="A4">
+            <v>2</v>
+          </cell>
+          <cell r="B4" t="str">
+            <v>{0} の満腹度が {1} 回復した</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="A5">
+            <v>3</v>
+          </cell>
+          <cell r="B5" t="str">
+            <v>{0} の {1}</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="A6">
+            <v>4</v>
+          </cell>
+          <cell r="B6" t="str">
+            <v>{0} は焼けてしまった</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="A7">
+            <v>5</v>
+          </cell>
+          <cell r="B7" t="str">
+            <v>{0} は腐ってしまった</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="A8">
+            <v>6</v>
+          </cell>
+          <cell r="B8" t="str">
+            <v>{0} を置いた</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="A9">
+            <v>7</v>
+          </cell>
+          <cell r="B9" t="str">
+            <v>{0} を置けなかった</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="A10">
+            <v>8</v>
+          </cell>
+          <cell r="B10" t="str">
+            <v>{0} を装備した</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="A11">
+            <v>9</v>
+          </cell>
+          <cell r="B11" t="str">
+            <v>{0} を外した</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="A12">
+            <v>10</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="A13">
+            <v>11</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="A14">
+            <v>12</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="A15">
+            <v>13</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="A16">
+            <v>1000</v>
+          </cell>
+          <cell r="B16" t="str">
+            <v>{0}を拾えなかった</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="A17">
+            <v>1001</v>
+          </cell>
+          <cell r="B17" t="str">
+            <v>{0}を拾った</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="A18">
+            <v>2000</v>
+          </cell>
+          <cell r="B18" t="str">
+            <v>ポーションA</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="A19">
+            <v>2100</v>
+          </cell>
+          <cell r="B19" t="str">
+            <v>肉</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="A20">
+            <v>2101</v>
+          </cell>
+          <cell r="B20" t="str">
+            <v>焼けた肉</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="A21">
+            <v>2102</v>
+          </cell>
+          <cell r="B21" t="str">
+            <v>腐った肉</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="A22">
+            <v>2103</v>
+          </cell>
+          <cell r="B22" t="str">
+            <v>黒焦げ肉</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="A23">
+            <v>2200</v>
+          </cell>
+          <cell r="B23" t="str">
+            <v>杖C</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="A24">
+            <v>2600</v>
+          </cell>
+          <cell r="B24" t="str">
+            <v>テスト武器</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="A25">
+            <v>2700</v>
+          </cell>
+          <cell r="B25" t="str">
+            <v>てすと防具</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="A26">
+            <v>10000</v>
+          </cell>
+          <cell r="B26" t="str">
+            <v>プレイヤー</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="A27">
+            <v>10001</v>
+          </cell>
+          <cell r="B27" t="str">
+            <v>グール</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="A28">
+            <v>10002</v>
+          </cell>
+          <cell r="B28" t="str">
+            <v>ハエ</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="A29">
+            <v>10003</v>
+          </cell>
+          <cell r="B29" t="str">
+            <v>スライム</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="A30">
+            <v>10004</v>
+          </cell>
+          <cell r="B30" t="str">
+            <v>ゾンビA</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="A31">
+            <v>10005</v>
+          </cell>
+          <cell r="B31" t="str">
+            <v>ゾンビB</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="A32">
+            <v>15000</v>
+          </cell>
+          <cell r="B32" t="str">
+            <v>攻撃</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="A33">
+            <v>15001</v>
+          </cell>
+          <cell r="B33" t="str">
+            <v>ポーションA</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="A34">
+            <v>15002</v>
+          </cell>
+          <cell r="B34" t="str">
+            <v>肉</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="A35">
+            <v>15003</v>
+          </cell>
+          <cell r="B35" t="str">
+            <v>杖C</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="A36">
+            <v>15004</v>
+          </cell>
+          <cell r="B36" t="str">
+            <v>炎</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="A37">
+            <v>15005</v>
+          </cell>
+          <cell r="B37" t="str">
+            <v>腐り攻撃</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="A38">
+            <v>15006</v>
+          </cell>
+          <cell r="B38" t="str">
+            <v>焼けた肉</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="A39">
+            <v>15007</v>
+          </cell>
+          <cell r="B39" t="str">
+            <v>黒焦げ肉</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="A40">
+            <v>20000</v>
+          </cell>
+          <cell r="B40" t="str">
+            <v>使う</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="A41">
+            <v>20001</v>
+          </cell>
+          <cell r="B41" t="str">
+            <v>置く</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="A42">
+            <v>20002</v>
+          </cell>
+          <cell r="B42" t="str">
+            <v>装備</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="A43">
+            <v>20003</v>
+          </cell>
+          <cell r="B43" t="str">
+            <v>外す</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="A44">
+            <v>20004</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -494,54 +859,58 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="4.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:11">
       <c r="A2" s="2">
         <v>0</v>
       </c>
@@ -549,19 +918,20 @@
         <f>2000+A2</f>
         <v>2000</v>
       </c>
-      <c r="C2" s="2">
-        <f>VLOOKUP(D2,reference!A:B,2,FALSE)</f>
+      <c r="C2" s="5" t="str">
+        <f>VLOOKUP(B2,[1]MessageData!$A:$B,2,FALSE)</f>
+        <v>ポーションA</v>
+      </c>
+      <c r="D2" s="2">
+        <f>VLOOKUP(E2,reference!A:B,2,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="2">
+      <c r="F2" s="2">
         <v>1</v>
       </c>
-      <c r="F2" s="2">
-        <v>-1</v>
-      </c>
       <c r="G2" s="2">
         <v>-1</v>
       </c>
@@ -571,11 +941,14 @@
       <c r="I2" s="2">
         <v>-1</v>
       </c>
-      <c r="J2" s="4">
+      <c r="J2" s="2">
+        <v>-1</v>
+      </c>
+      <c r="K2" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:11">
       <c r="A3" s="2">
         <v>100</v>
       </c>
@@ -583,33 +956,37 @@
         <f t="shared" ref="B3:B7" si="0">2000+A3</f>
         <v>2100</v>
       </c>
-      <c r="C3" s="2">
-        <f>VLOOKUP(D3,reference!A:B,2,FALSE)</f>
+      <c r="C3" s="5" t="str">
+        <f>VLOOKUP(B3,[1]MessageData!$A:$B,2,FALSE)</f>
+        <v>肉</v>
+      </c>
+      <c r="D3" s="2">
+        <f>VLOOKUP(E3,reference!A:B,2,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="2">
+      <c r="F3" s="2">
         <v>2</v>
       </c>
-      <c r="F3" s="2">
-        <v>-1</v>
-      </c>
       <c r="G3" s="2">
         <v>-1</v>
       </c>
       <c r="H3" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I3" s="2">
         <v>101</v>
       </c>
-      <c r="I3" s="2">
+      <c r="J3" s="2">
         <v>102</v>
       </c>
-      <c r="J3" s="4">
+      <c r="K3" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:11">
       <c r="A4" s="2">
         <v>101</v>
       </c>
@@ -617,33 +994,37 @@
         <f t="shared" ref="B4" si="1">2000+A4</f>
         <v>2101</v>
       </c>
-      <c r="C4" s="2">
-        <f>VLOOKUP(D4,reference!A:B,2,FALSE)</f>
+      <c r="C4" s="5" t="str">
+        <f>VLOOKUP(B4,[1]MessageData!$A:$B,2,FALSE)</f>
+        <v>焼けた肉</v>
+      </c>
+      <c r="D4" s="2">
+        <f>VLOOKUP(E4,reference!A:B,2,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="2">
+      <c r="F4" s="2">
         <v>6</v>
       </c>
-      <c r="F4" s="2">
-        <v>-1</v>
-      </c>
       <c r="G4" s="2">
         <v>-1</v>
       </c>
       <c r="H4" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I4" s="2">
         <v>103</v>
       </c>
-      <c r="I4" s="2">
+      <c r="J4" s="2">
         <v>102</v>
       </c>
-      <c r="J4" s="4">
+      <c r="K4" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:11">
       <c r="A5" s="2">
         <v>102</v>
       </c>
@@ -651,33 +1032,37 @@
         <f t="shared" ref="B5" si="2">2000+A5</f>
         <v>2102</v>
       </c>
-      <c r="C5" s="2">
-        <f>VLOOKUP(D5,reference!A:B,2,FALSE)</f>
+      <c r="C5" s="5" t="str">
+        <f>VLOOKUP(B5,[1]MessageData!$A:$B,2,FALSE)</f>
+        <v>腐った肉</v>
+      </c>
+      <c r="D5" s="2">
+        <f>VLOOKUP(E5,reference!A:B,2,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="2">
+      <c r="F5" s="2">
         <v>6</v>
       </c>
-      <c r="F5" s="2">
-        <v>-1</v>
-      </c>
       <c r="G5" s="2">
         <v>-1</v>
       </c>
       <c r="H5" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I5" s="2">
         <v>101</v>
       </c>
-      <c r="I5" s="2">
-        <v>-1</v>
-      </c>
-      <c r="J5" s="4">
+      <c r="J5" s="2">
+        <v>-1</v>
+      </c>
+      <c r="K5" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:11">
       <c r="A6" s="2">
         <v>103</v>
       </c>
@@ -685,19 +1070,20 @@
         <f t="shared" ref="B6" si="3">2000+A6</f>
         <v>2103</v>
       </c>
-      <c r="C6" s="2">
-        <f>VLOOKUP(D6,reference!A:B,2,FALSE)</f>
+      <c r="C6" s="5" t="str">
+        <f>VLOOKUP(B6,[1]MessageData!$A:$B,2,FALSE)</f>
+        <v>黒焦げ肉</v>
+      </c>
+      <c r="D6" s="2">
+        <f>VLOOKUP(E6,reference!A:B,2,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="2">
+      <c r="F6" s="2">
         <v>7</v>
       </c>
-      <c r="F6" s="2">
-        <v>-1</v>
-      </c>
       <c r="G6" s="2">
         <v>-1</v>
       </c>
@@ -705,13 +1091,16 @@
         <v>-1</v>
       </c>
       <c r="I6" s="2">
+        <v>-1</v>
+      </c>
+      <c r="J6" s="2">
         <v>102</v>
       </c>
-      <c r="J6" s="4">
+      <c r="K6" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:11">
       <c r="A7" s="2">
         <v>200</v>
       </c>
@@ -719,33 +1108,37 @@
         <f t="shared" si="0"/>
         <v>2200</v>
       </c>
-      <c r="C7" s="2">
-        <f>VLOOKUP(D7,reference!A:B,2,FALSE)</f>
+      <c r="C7" s="5" t="str">
+        <f>VLOOKUP(B7,[1]MessageData!$A:$B,2,FALSE)</f>
+        <v>杖C</v>
+      </c>
+      <c r="D7" s="2">
+        <f>VLOOKUP(E7,reference!A:B,2,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>5</v>
-      </c>
-      <c r="E7" s="2">
-        <v>3</v>
       </c>
       <c r="F7" s="2">
         <v>3</v>
       </c>
       <c r="G7" s="2">
+        <v>3</v>
+      </c>
+      <c r="H7" s="2">
         <v>7</v>
       </c>
-      <c r="H7" s="2">
-        <v>-1</v>
-      </c>
       <c r="I7" s="2">
         <v>-1</v>
       </c>
-      <c r="J7" s="4">
+      <c r="J7" s="2">
+        <v>-1</v>
+      </c>
+      <c r="K7" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:11">
       <c r="A8" s="2">
         <v>600</v>
       </c>
@@ -753,16 +1146,17 @@
         <f t="shared" ref="B8" si="4">2000+A8</f>
         <v>2600</v>
       </c>
-      <c r="C8" s="2">
-        <f>VLOOKUP(D8,reference!A:B,2,FALSE)</f>
+      <c r="C8" s="5" t="str">
+        <f>VLOOKUP(B8,[1]MessageData!$A:$B,2,FALSE)</f>
+        <v>テスト武器</v>
+      </c>
+      <c r="D8" s="2">
+        <f>VLOOKUP(E8,reference!A:B,2,FALSE)</f>
         <v>6</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="2">
-        <v>-1</v>
-      </c>
       <c r="F8" s="2">
         <v>-1</v>
       </c>
@@ -775,11 +1169,14 @@
       <c r="I8" s="2">
         <v>-1</v>
       </c>
-      <c r="J8" s="4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
+      <c r="J8" s="2">
+        <v>-1</v>
+      </c>
+      <c r="K8" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
       <c r="A9" s="2">
         <v>700</v>
       </c>
@@ -787,16 +1184,17 @@
         <f t="shared" ref="B9" si="5">2000+A9</f>
         <v>2700</v>
       </c>
-      <c r="C9" s="2">
-        <f>VLOOKUP(D9,reference!A:B,2,FALSE)</f>
+      <c r="C9" s="5" t="str">
+        <f>VLOOKUP(B9,[1]MessageData!$A:$B,2,FALSE)</f>
+        <v>てすと防具</v>
+      </c>
+      <c r="D9" s="2">
+        <f>VLOOKUP(E9,reference!A:B,2,FALSE)</f>
         <v>7</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E9" s="2">
-        <v>-1</v>
-      </c>
       <c r="F9" s="2">
         <v>-1</v>
       </c>
@@ -809,8 +1207,11 @@
       <c r="I9" s="2">
         <v>-1</v>
       </c>
-      <c r="J9" s="4">
-        <v>2</v>
+      <c r="J9" s="2">
+        <v>-1</v>
+      </c>
+      <c r="K9" s="4">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -824,7 +1225,7 @@
           <x14:formula1>
             <xm:f>reference!$A:$A</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D9</xm:sqref>
+          <xm:sqref>E2:E9</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
